--- a/src/test/resources/filters_personal_details/filters_category.xlsx
+++ b/src/test/resources/filters_personal_details/filters_category.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\Eticaa Project Automation\Eticaa-Automation\src\test\resources\filters_personal_details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA75CEB-4055-4EA7-AA4B-134092725C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE675C28-305B-4868-BA68-98A44C9DFB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Locations" sheetId="1" r:id="rId1"/>
+    <sheet name="CategoryFilters" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -393,39 +404,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
